--- a/back/femr_v12_internal.xlsx
+++ b/back/femr_v12_internal.xlsx
@@ -403,11 +403,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -632,11 +648,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -861,11 +893,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -1090,11 +1138,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -1319,11 +1383,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -1548,11 +1628,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -1777,11 +1873,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -2006,11 +2118,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -2235,11 +2363,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -2464,11 +2608,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -2693,11 +2853,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -2922,11 +3098,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -3151,11 +3343,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -3380,11 +3588,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -3609,11 +3833,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -3838,11 +4078,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -4067,11 +4323,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -4296,11 +4568,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -4525,11 +4813,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -4754,11 +5058,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -4983,11 +5303,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -5212,11 +5548,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -5441,11 +5793,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -5670,11 +6038,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -5899,11 +6283,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -6128,11 +6528,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -6357,11 +6773,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -6586,11 +7018,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -6815,11 +7263,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -7044,11 +7508,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -7273,11 +7753,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -7502,11 +7998,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -7731,11 +8243,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -7960,11 +8488,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -8189,11 +8733,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -8418,11 +8978,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -8647,11 +9223,27 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -8685,7 +9277,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -8712,7 +9304,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -8739,7 +9331,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -8766,7 +9358,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -8793,7 +9385,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -8820,7 +9412,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -8847,7 +9439,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -8874,7 +9466,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -8901,7 +9493,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -8928,7 +9520,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -8955,7 +9547,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -8982,7 +9574,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -9009,7 +9601,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -9036,7 +9628,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -9063,7 +9655,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -9090,7 +9682,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -9117,7 +9709,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -9144,7 +9736,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -9171,7 +9763,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -9198,7 +9790,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -9225,7 +9817,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -9252,7 +9844,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -9279,7 +9871,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -9306,7 +9898,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -9333,7 +9925,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -9360,7 +9952,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -9387,7 +9979,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -9414,7 +10006,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -9441,7 +10033,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -9468,7 +10060,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -9495,7 +10087,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -9522,7 +10114,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -9549,7 +10141,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -9576,7 +10168,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -9603,7 +10195,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -9630,7 +10222,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -9657,7 +10249,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="15120000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -10362,6 +10954,9 @@
       <c r="AA18" s="2" t="n">
         <v>3951.75</v>
       </c>
+      <c r="AB18" s="2" t="n">
+        <v>8837.07</v>
+      </c>
       <c r="AE18" s="10">
         <f>SUM(C18:AD18)</f>
         <v/>
@@ -10397,6 +10992,9 @@
       <c r="AA19" s="2" t="n">
         <v>2139.08</v>
       </c>
+      <c r="AB19" s="2" t="n">
+        <v>4741.58</v>
+      </c>
       <c r="AE19" s="10">
         <f>SUM(C19:AD19)</f>
         <v/>
@@ -10600,6 +11198,9 @@
       <c r="AA29" s="2" t="n">
         <v>8490.110000000001</v>
       </c>
+      <c r="AB29" s="2" t="n">
+        <v>18396.74</v>
+      </c>
       <c r="AE29" s="10">
         <f>SUM(C29:AD29)</f>
         <v/>
@@ -11163,142 +11764,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -12976,142 +13577,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -14129,6 +14730,9 @@
       <c r="AA18" s="2" t="n">
         <v>12568.42</v>
       </c>
+      <c r="AB18" s="2" t="n">
+        <v>6179.52</v>
+      </c>
       <c r="AE18" s="10">
         <f>SUM(C18:AD18)</f>
         <v/>
@@ -14164,6 +14768,9 @@
       <c r="AA19" s="2" t="n">
         <v>6803.3</v>
       </c>
+      <c r="AB19" s="2" t="n">
+        <v>3345.02</v>
+      </c>
       <c r="AE19" s="10">
         <f>SUM(C19:AD19)</f>
         <v/>
@@ -14316,6 +14923,9 @@
       <c r="AA29" s="2" t="n">
         <v>26395.91</v>
       </c>
+      <c r="AB29" s="2" t="n">
+        <v>11803.5</v>
+      </c>
       <c r="AE29" s="10">
         <f>SUM(C29:AD29)</f>
         <v/>
@@ -14879,142 +15489,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -16026,6 +16636,9 @@
       <c r="Y18" s="2" t="n">
         <v>429.13</v>
       </c>
+      <c r="AB18" s="2" t="n">
+        <v>90.15000000000001</v>
+      </c>
       <c r="AE18" s="10">
         <f>SUM(C18:AD18)</f>
         <v/>
@@ -16055,6 +16668,9 @@
       <c r="Y19" s="2" t="n">
         <v>215.68</v>
       </c>
+      <c r="AB19" s="2" t="n">
+        <v>48.8</v>
+      </c>
       <c r="AE19" s="10">
         <f>SUM(C19:AD19)</f>
         <v/>
@@ -16186,6 +16802,9 @@
       <c r="Y29" s="2" t="n">
         <v>856.24</v>
       </c>
+      <c r="AB29" s="2" t="n">
+        <v>189.33</v>
+      </c>
       <c r="AE29" s="10">
         <f>SUM(C29:AD29)</f>
         <v/>
@@ -16749,142 +17368,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -17896,6 +18515,9 @@
       <c r="Y18" s="2" t="n">
         <v>13968.49</v>
       </c>
+      <c r="AB18" s="2" t="n">
+        <v>991.38</v>
+      </c>
       <c r="AE18" s="10">
         <f>SUM(C18:AD18)</f>
         <v/>
@@ -17925,6 +18547,9 @@
       <c r="Y19" s="2" t="n">
         <v>7020.56</v>
       </c>
+      <c r="AB19" s="2" t="n">
+        <v>536.6</v>
+      </c>
       <c r="AE19" s="10">
         <f>SUM(C19:AD19)</f>
         <v/>
@@ -17976,6 +18601,9 @@
       <c r="Y22" s="2" t="n">
         <v>12787.5</v>
       </c>
+      <c r="AB22" s="2" t="n">
+        <v>3900</v>
+      </c>
       <c r="AE22" s="10">
         <f>SUM(C22:AD22)</f>
         <v/>
@@ -18077,6 +18705,9 @@
       <c r="Y29" s="2" t="n">
         <v>21218.43</v>
       </c>
+      <c r="AB29" s="2" t="n">
+        <v>4695.69</v>
+      </c>
       <c r="AE29" s="10">
         <f>SUM(C29:AD29)</f>
         <v/>
@@ -18640,142 +19271,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -20453,142 +21084,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -22266,142 +22897,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -24079,142 +24710,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -25895,142 +26526,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -27712,142 +28343,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -29529,142 +30160,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -30682,6 +31313,9 @@
       <c r="AA18" s="2" t="n">
         <v>1800.97</v>
       </c>
+      <c r="AB18" s="2" t="n">
+        <v>2493.15</v>
+      </c>
       <c r="AE18" s="10">
         <f>SUM(C18:AD18)</f>
         <v/>
@@ -30717,6 +31351,9 @@
       <c r="AA19" s="2" t="n">
         <v>974.87</v>
       </c>
+      <c r="AB19" s="2" t="n">
+        <v>1603.38</v>
+      </c>
       <c r="AE19" s="10">
         <f>SUM(C19:AD19)</f>
         <v/>
@@ -30857,6 +31494,9 @@
       <c r="AA29" s="2" t="n">
         <v>3782.35</v>
       </c>
+      <c r="AB29" s="2" t="n">
+        <v>6220.92</v>
+      </c>
       <c r="AE29" s="10">
         <f>SUM(C29:AD29)</f>
         <v/>
@@ -31420,142 +32060,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -33237,142 +33877,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -35057,142 +35697,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -36877,142 +37517,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -38694,142 +39334,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -40511,142 +41151,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -42328,142 +42968,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -44145,142 +44785,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -45958,142 +46598,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -47775,142 +48415,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -49592,142 +50232,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -50745,6 +51385,9 @@
       <c r="AA18" s="2" t="n">
         <v>14892.9</v>
       </c>
+      <c r="AB18" s="2" t="n">
+        <v>7886.37</v>
+      </c>
       <c r="AE18" s="10">
         <f>SUM(C18:AD18)</f>
         <v/>
@@ -50780,6 +51423,9 @@
       <c r="AA19" s="2" t="n">
         <v>8061.53</v>
       </c>
+      <c r="AB19" s="2" t="n">
+        <v>4268.83</v>
+      </c>
       <c r="AE19" s="10">
         <f>SUM(C19:AD19)</f>
         <v/>
@@ -50876,6 +51522,9 @@
       <c r="AA25" s="2" t="n">
         <v>17657.02</v>
       </c>
+      <c r="AB25" s="2" t="n">
+        <v>2009.38</v>
+      </c>
       <c r="AE25" s="10">
         <f>SUM(C25:AD25)</f>
         <v/>
@@ -50944,6 +51593,9 @@
       <c r="AA29" s="2" t="n">
         <v>67602.08</v>
       </c>
+      <c r="AB29" s="2" t="n">
+        <v>19300.5</v>
+      </c>
       <c r="AE29" s="10">
         <f>SUM(C29:AD29)</f>
         <v/>
@@ -51507,142 +52159,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -53324,142 +53976,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -55141,142 +55793,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -56958,142 +57610,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -58775,142 +59427,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -60594,142 +61246,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -62411,142 +63063,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -64228,142 +64880,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -66045,142 +66697,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -67192,6 +67844,9 @@
       <c r="AA18" s="2" t="n">
         <v>191</v>
       </c>
+      <c r="AB18" s="2" t="n">
+        <v>2676.39</v>
+      </c>
       <c r="AE18" s="10">
         <f>SUM(C18:AD18)</f>
         <v/>
@@ -67221,6 +67876,9 @@
       <c r="AA19" s="2" t="n">
         <v>103.39</v>
       </c>
+      <c r="AB19" s="2" t="n">
+        <v>1448.71</v>
+      </c>
       <c r="AE19" s="10">
         <f>SUM(C19:AD19)</f>
         <v/>
@@ -67323,6 +67981,9 @@
       <c r="Z25" s="2" t="n">
         <v>-5200</v>
       </c>
+      <c r="AB25" s="2" t="n">
+        <v>5160</v>
+      </c>
       <c r="AE25" s="10">
         <f>SUM(C25:AD25)</f>
         <v/>
@@ -67400,6 +68061,9 @@
       <c r="AA29" s="2" t="n">
         <v>2322</v>
       </c>
+      <c r="AB29" s="2" t="n">
+        <v>12651.84</v>
+      </c>
       <c r="AE29" s="10">
         <f>SUM(C29:AD29)</f>
         <v/>
@@ -67963,142 +68627,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -69851,142 +70515,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -70995,6 +71659,9 @@
       <c r="Y18" s="2" t="n">
         <v>259.56</v>
       </c>
+      <c r="AB18" s="2" t="n">
+        <v>100.96</v>
+      </c>
       <c r="AE18" s="10">
         <f>SUM(C18:AD18)</f>
         <v/>
@@ -71021,6 +71688,9 @@
       <c r="Y19" s="2" t="n">
         <v>130.45</v>
       </c>
+      <c r="AB19" s="2" t="n">
+        <v>54.65</v>
+      </c>
       <c r="AE19" s="10">
         <f>SUM(C19:AD19)</f>
         <v/>
@@ -71146,6 +71816,9 @@
       <c r="Y29" s="2" t="n">
         <v>517.89</v>
       </c>
+      <c r="AB29" s="2" t="n">
+        <v>212.03</v>
+      </c>
       <c r="AE29" s="10">
         <f>SUM(C29:AD29)</f>
         <v/>
@@ -71709,142 +72382,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -73594,142 +74267,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -74741,6 +75414,9 @@
       <c r="Y18" s="2" t="n">
         <v>51884.92</v>
       </c>
+      <c r="AB18" s="2" t="n">
+        <v>5308.24</v>
+      </c>
       <c r="AE18" s="10">
         <f>SUM(C18:AD18)</f>
         <v/>
@@ -74770,6 +75446,9 @@
       <c r="Y19" s="2" t="n">
         <v>26077.38</v>
       </c>
+      <c r="AB19" s="2" t="n">
+        <v>2873.46</v>
+      </c>
       <c r="AE19" s="10">
         <f>SUM(C19:AD19)</f>
         <v/>
@@ -74913,6 +75592,9 @@
       <c r="Y29" s="2" t="n">
         <v>103526.15</v>
       </c>
+      <c r="AB29" s="2" t="n">
+        <v>11148.64</v>
+      </c>
       <c r="AE29" s="10">
         <f>SUM(C29:AD29)</f>
         <v/>
@@ -75476,142 +76158,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
@@ -77343,142 +78025,142 @@
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY20</t>
+          <t>Q1 FY20</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY20</t>
+          <t>Q2 FY20</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY20</t>
+          <t>Q3 FY20</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY20</t>
+          <t>Q4 FY20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY21</t>
+          <t>Q1 FY21</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY21</t>
+          <t>Q2 FY21</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY21</t>
+          <t>Q3 FY21</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY21</t>
+          <t>Q4 FY21</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY22</t>
+          <t>Q1 FY22</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY22</t>
+          <t>Q2 FY22</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY22</t>
+          <t>Q3 FY22</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY22</t>
+          <t>Q4 FY22</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY23</t>
+          <t>Q1 FY23</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY23</t>
+          <t>Q2 FY23</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY23</t>
+          <t>Q3 FY23</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY23</t>
+          <t>Q4 FY23</t>
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY24</t>
+          <t>Q1 FY24</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY24</t>
+          <t>Q2 FY24</t>
         </is>
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY24</t>
+          <t>Q3 FY24</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY24</t>
+          <t>Q4 FY24</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY25</t>
+          <t>Q1 FY25</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY25</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY25</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY25</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="Z51" s="11" t="inlineStr">
         <is>
-          <t>Q1 FY26</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="AA51" s="11" t="inlineStr">
         <is>
-          <t>Q2 FY26</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="AB51" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="AC51" s="11" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q4 FY26</t>
         </is>
       </c>
     </row>
